--- a/data/nzd0051/nzd0051.xlsx
+++ b/data/nzd0051/nzd0051.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J568"/>
+  <dimension ref="A1:J574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20886,6 +20886,222 @@
         <v>395.73</v>
       </c>
       <c r="J568" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:16:59+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>381.68</v>
+      </c>
+      <c r="C569" t="n">
+        <v>388.71</v>
+      </c>
+      <c r="D569" t="n">
+        <v>393.42</v>
+      </c>
+      <c r="E569" t="n">
+        <v>400.52</v>
+      </c>
+      <c r="F569" t="n">
+        <v>395.03</v>
+      </c>
+      <c r="G569" t="n">
+        <v>396.22</v>
+      </c>
+      <c r="H569" t="n">
+        <v>398.03</v>
+      </c>
+      <c r="I569" t="n">
+        <v>395.46</v>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>381.71</v>
+      </c>
+      <c r="C570" t="n">
+        <v>388.49</v>
+      </c>
+      <c r="D570" t="n">
+        <v>393.52</v>
+      </c>
+      <c r="E570" t="n">
+        <v>400.3</v>
+      </c>
+      <c r="F570" t="n">
+        <v>395.04</v>
+      </c>
+      <c r="G570" t="n">
+        <v>395.79</v>
+      </c>
+      <c r="H570" t="n">
+        <v>397.57</v>
+      </c>
+      <c r="I570" t="n">
+        <v>396.19</v>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>382.16</v>
+      </c>
+      <c r="C571" t="n">
+        <v>388.72</v>
+      </c>
+      <c r="D571" t="n">
+        <v>393.52</v>
+      </c>
+      <c r="E571" t="n">
+        <v>400.52</v>
+      </c>
+      <c r="F571" t="n">
+        <v>395.31</v>
+      </c>
+      <c r="G571" t="n">
+        <v>396.02</v>
+      </c>
+      <c r="H571" t="n">
+        <v>397.38</v>
+      </c>
+      <c r="I571" t="n">
+        <v>396.52</v>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>382.85</v>
+      </c>
+      <c r="C572" t="n">
+        <v>389.11</v>
+      </c>
+      <c r="D572" t="n">
+        <v>393.6</v>
+      </c>
+      <c r="E572" t="n">
+        <v>400.57</v>
+      </c>
+      <c r="F572" t="n">
+        <v>395.61</v>
+      </c>
+      <c r="G572" t="n">
+        <v>396.17</v>
+      </c>
+      <c r="H572" t="n">
+        <v>397.63</v>
+      </c>
+      <c r="I572" t="n">
+        <v>397.05</v>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>383.05</v>
+      </c>
+      <c r="C573" t="n">
+        <v>389.92</v>
+      </c>
+      <c r="D573" t="n">
+        <v>393.8</v>
+      </c>
+      <c r="E573" t="n">
+        <v>401.04</v>
+      </c>
+      <c r="F573" t="n">
+        <v>395.78</v>
+      </c>
+      <c r="G573" t="n">
+        <v>396.62</v>
+      </c>
+      <c r="H573" t="n">
+        <v>397.94</v>
+      </c>
+      <c r="I573" t="n">
+        <v>397.02</v>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>383.77</v>
+      </c>
+      <c r="C574" t="n">
+        <v>391.27</v>
+      </c>
+      <c r="D574" t="n">
+        <v>395.41</v>
+      </c>
+      <c r="E574" t="n">
+        <v>402.63</v>
+      </c>
+      <c r="F574" t="n">
+        <v>397.16</v>
+      </c>
+      <c r="G574" t="n">
+        <v>397.64</v>
+      </c>
+      <c r="H574" t="n">
+        <v>398.09</v>
+      </c>
+      <c r="I574" t="n">
+        <v>396.98</v>
+      </c>
+      <c r="J574" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20902,7 +21118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B593"/>
+  <dimension ref="A1:B599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26835,6 +27051,66 @@
       </c>
       <c r="B593" t="n">
         <v>0.87</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B594" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B595" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B596" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B598" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B599" t="n">
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>
@@ -27003,28 +27279,28 @@
         <v>0.097</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1154560388292048</v>
+        <v>0.1123316155287338</v>
       </c>
       <c r="J2" t="n">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="K2" t="n">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03489063845386031</v>
+        <v>0.03380174520453882</v>
       </c>
       <c r="M2" t="n">
-        <v>3.748670136134872</v>
+        <v>3.72293703252317</v>
       </c>
       <c r="N2" t="n">
-        <v>21.27449176104803</v>
+        <v>21.08179554002036</v>
       </c>
       <c r="O2" t="n">
-        <v>4.612427968114845</v>
+        <v>4.591491646515363</v>
       </c>
       <c r="P2" t="n">
-        <v>380.972378974525</v>
+        <v>381.0049418246898</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27081,28 +27357,28 @@
         <v>0.1099</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1788049192186768</v>
+        <v>0.1751885012600314</v>
       </c>
       <c r="J3" t="n">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="K3" t="n">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1473032702599949</v>
+        <v>0.1446396663535081</v>
       </c>
       <c r="M3" t="n">
-        <v>2.527726758338429</v>
+        <v>2.520973001748963</v>
       </c>
       <c r="N3" t="n">
-        <v>10.67823341406771</v>
+        <v>10.6083869355956</v>
       </c>
       <c r="O3" t="n">
-        <v>3.267756633237504</v>
+        <v>3.257051877940479</v>
       </c>
       <c r="P3" t="n">
-        <v>386.3439937663563</v>
+        <v>386.3816845456823</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27159,28 +27435,28 @@
         <v>0.1301</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1519690382825678</v>
+        <v>0.1501679087076671</v>
       </c>
       <c r="J4" t="n">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="K4" t="n">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1356824877159787</v>
+        <v>0.1354561813149546</v>
       </c>
       <c r="M4" t="n">
-        <v>1.871994862934969</v>
+        <v>1.862542930478229</v>
       </c>
       <c r="N4" t="n">
-        <v>8.488247232286758</v>
+        <v>8.41238053096451</v>
       </c>
       <c r="O4" t="n">
-        <v>2.913459667180371</v>
+        <v>2.900410407332816</v>
       </c>
       <c r="P4" t="n">
-        <v>390.6785761778191</v>
+        <v>390.6973452958159</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27237,28 +27513,28 @@
         <v>0.1363</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1970828710929709</v>
+        <v>0.192902318608848</v>
       </c>
       <c r="J5" t="n">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="K5" t="n">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2291481329929358</v>
+        <v>0.2245798384663924</v>
       </c>
       <c r="M5" t="n">
-        <v>2.217194250987706</v>
+        <v>2.215360852965937</v>
       </c>
       <c r="N5" t="n">
-        <v>7.538946161321895</v>
+        <v>7.509615158656067</v>
       </c>
       <c r="O5" t="n">
-        <v>2.745714144138442</v>
+        <v>2.740367705008959</v>
       </c>
       <c r="P5" t="n">
-        <v>397.6876274698502</v>
+        <v>397.7312043327744</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27315,28 +27591,28 @@
         <v>0.1141</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09670868354059062</v>
+        <v>0.09450770789450512</v>
       </c>
       <c r="J6" t="n">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="K6" t="n">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06313417937990673</v>
+        <v>0.06168416838932811</v>
       </c>
       <c r="M6" t="n">
-        <v>2.309243862841196</v>
+        <v>2.296517045549573</v>
       </c>
       <c r="N6" t="n">
-        <v>8.007594517439186</v>
+        <v>7.941202175466384</v>
       </c>
       <c r="O6" t="n">
-        <v>2.829769339970872</v>
+        <v>2.818013870701559</v>
       </c>
       <c r="P6" t="n">
-        <v>394.1395775348355</v>
+        <v>394.162513694085</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27393,28 +27669,28 @@
         <v>0.1124</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02048297944086226</v>
+        <v>0.01772994132561273</v>
       </c>
       <c r="J7" t="n">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="K7" t="n">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002577977032903411</v>
+        <v>0.001973818711146436</v>
       </c>
       <c r="M7" t="n">
-        <v>2.469945226485838</v>
+        <v>2.457620500215025</v>
       </c>
       <c r="N7" t="n">
-        <v>9.365790585640701</v>
+        <v>9.29021429385541</v>
       </c>
       <c r="O7" t="n">
-        <v>3.060357917897954</v>
+        <v>3.047985284389577</v>
       </c>
       <c r="P7" t="n">
-        <v>397.2174045840059</v>
+        <v>397.2461004873239</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27471,28 +27747,28 @@
         <v>0.0858</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00194680012822205</v>
+        <v>0.001906911650719033</v>
       </c>
       <c r="J8" t="n">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="K8" t="n">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="L8" t="n">
-        <v>2.322483676220344e-05</v>
+        <v>2.280983114788526e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.392404243964309</v>
+        <v>2.369886285500316</v>
       </c>
       <c r="N8" t="n">
-        <v>9.430710244457108</v>
+        <v>9.332507063605497</v>
       </c>
       <c r="O8" t="n">
-        <v>3.070946148088095</v>
+        <v>3.054915230183237</v>
       </c>
       <c r="P8" t="n">
-        <v>397.7410686847547</v>
+        <v>397.7414830850165</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27549,28 +27825,28 @@
         <v>0.0939</v>
       </c>
       <c r="I9" t="n">
-        <v>0.007221891136282774</v>
+        <v>0.004109521828181092</v>
       </c>
       <c r="J9" t="n">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="K9" t="n">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="L9" t="n">
-        <v>0.000286236730350331</v>
+        <v>9.465294480437425e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>2.541863019803412</v>
+        <v>2.525231779993881</v>
       </c>
       <c r="N9" t="n">
-        <v>10.52729055649735</v>
+        <v>10.44423183527901</v>
       </c>
       <c r="O9" t="n">
-        <v>3.244578640824931</v>
+        <v>3.231753678001931</v>
       </c>
       <c r="P9" t="n">
-        <v>397.8778197332722</v>
+        <v>397.9102417626843</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27608,7 +27884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J568"/>
+  <dimension ref="A1:J574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57139,6 +57415,318 @@
         </is>
       </c>
     </row>
+    <row r="569">
+      <c r="A569" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:16:59+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>-35.02107391828762,173.86593934393946</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>-35.02096339051106,173.86682560857204</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>-35.020849214415044,173.86770673759057</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>-35.02070928291306,173.86854130047183</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>-35.02052421156835,173.8693551540911</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>-35.020247463069964,173.87013321130124</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>-35.019864581073044,173.8707991219626</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>-35.0193670122008,173.87135736366557</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>-35.02107364845931,173.86593932075556</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>-35.020965366576405,173.86682581961543</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>-35.02084831843675,173.86770661461608</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>-35.02071121260963,173.86854185917358</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>-35.02052412768996,173.8693551138751</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>-35.020250861472526,173.8701354800577</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>-35.01986766796228,173.87080248944352</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>-35.019362749891414,173.8713512666375</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>-35.02106960103469,173.86593897299707</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>-35.02096330068991,173.86682559897915</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>-35.02084831843675,173.86770661461608</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>-35.02070928291306,173.86854130047183</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>-35.02052186297363,173.86935402804295</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>-35.020249043722316,173.87013426653678</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>-35.01986894298172,173.8708038803596</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>-35.01936082309391,173.87134851044692</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>-35.02106339498362,173.86593843976746</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>-35.02095979766501,173.8668252248568</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>-35.02084760165411,173.8677065162365</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>-35.020708844345656,173.86854117349418</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>-35.02051934662215,173.8693528215628</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>-35.02024785823305,173.87013347511012</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>-35.01986726532456,173.87080205020686</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>-35.01935772854022,173.8713440838381</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>-35.021061596128234,173.86593828520816</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>-35.020952522151724,173.86682444783358</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>-35.02084580969754,173.86770627028756</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>-35.02070472181207,173.86853997990423</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>-35.02051792068965,173.86935213789076</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>-35.02024430176519,173.8701311008303</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>-35.01986518502963,173.87079978081755</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>-35.01935790370364,173.87134433440087</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>-35.021055120248825,173.86593772879482</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>-35.0209403962962,173.8668231527952</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>-35.020831384447,173.86770429039902</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>-35.02069077536852,173.8685359420158</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>-35.02050634547258,173.8693465880834</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>-35.02023624043788,173.87012571913007</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>-35.01986417843531,173.870798682726</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>-35.01935813725487,173.87134466848454</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0051/nzd0051.xlsx
+++ b/data/nzd0051/nzd0051.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J574"/>
+  <dimension ref="A1:J577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21104,6 +21104,114 @@
       <c r="J574" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>384.47</v>
+      </c>
+      <c r="C575" t="n">
+        <v>391.67</v>
+      </c>
+      <c r="D575" t="n">
+        <v>395.69</v>
+      </c>
+      <c r="E575" t="n">
+        <v>403.14</v>
+      </c>
+      <c r="F575" t="n">
+        <v>397.29</v>
+      </c>
+      <c r="G575" t="n">
+        <v>398.15</v>
+      </c>
+      <c r="H575" t="n">
+        <v>398.32</v>
+      </c>
+      <c r="I575" t="n">
+        <v>397.37</v>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>384.76</v>
+      </c>
+      <c r="C576" t="n">
+        <v>392.25</v>
+      </c>
+      <c r="D576" t="n">
+        <v>395.84</v>
+      </c>
+      <c r="E576" t="n">
+        <v>403.62</v>
+      </c>
+      <c r="F576" t="n">
+        <v>397.7</v>
+      </c>
+      <c r="G576" t="n">
+        <v>398.44</v>
+      </c>
+      <c r="H576" t="n">
+        <v>398.69</v>
+      </c>
+      <c r="I576" t="n">
+        <v>397.61</v>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>385.2</v>
+      </c>
+      <c r="C577" t="n">
+        <v>392.33</v>
+      </c>
+      <c r="D577" t="n">
+        <v>395.75</v>
+      </c>
+      <c r="E577" t="n">
+        <v>403.81</v>
+      </c>
+      <c r="F577" t="n">
+        <v>397.78</v>
+      </c>
+      <c r="G577" t="n">
+        <v>398.62</v>
+      </c>
+      <c r="H577" t="n">
+        <v>399</v>
+      </c>
+      <c r="I577" t="n">
+        <v>397.62</v>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -21118,7 +21226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B599"/>
+  <dimension ref="A1:B602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27111,6 +27219,36 @@
       </c>
       <c r="B599" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B600" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B602" t="n">
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
@@ -27279,28 +27417,28 @@
         <v>0.097</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1123316155287338</v>
+        <v>0.1131089991672911</v>
       </c>
       <c r="J2" t="n">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="K2" t="n">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03380174520453882</v>
+        <v>0.03463157815711515</v>
       </c>
       <c r="M2" t="n">
-        <v>3.72293703252317</v>
+        <v>3.708162225569205</v>
       </c>
       <c r="N2" t="n">
-        <v>21.08179554002036</v>
+        <v>20.97552256079195</v>
       </c>
       <c r="O2" t="n">
-        <v>4.591491646515363</v>
+        <v>4.579904208691701</v>
       </c>
       <c r="P2" t="n">
-        <v>381.0049418246898</v>
+        <v>380.9968094008959</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27357,28 +27495,28 @@
         <v>0.1099</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1751885012600314</v>
+        <v>0.1761642840172432</v>
       </c>
       <c r="J3" t="n">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="K3" t="n">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1446396663535081</v>
+        <v>0.1473948839637066</v>
       </c>
       <c r="M3" t="n">
-        <v>2.520973001748963</v>
+        <v>2.51264653933436</v>
       </c>
       <c r="N3" t="n">
-        <v>10.6083869355956</v>
+        <v>10.55841954825643</v>
       </c>
       <c r="O3" t="n">
-        <v>3.257051877940479</v>
+        <v>3.249372177553139</v>
       </c>
       <c r="P3" t="n">
-        <v>386.3816845456823</v>
+        <v>386.3714781211385</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27435,28 +27573,28 @@
         <v>0.1301</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1501679087076671</v>
+        <v>0.1511834056145392</v>
       </c>
       <c r="J4" t="n">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="K4" t="n">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1354561813149546</v>
+        <v>0.1383316522119623</v>
       </c>
       <c r="M4" t="n">
-        <v>1.862542930478229</v>
+        <v>1.858781868503596</v>
       </c>
       <c r="N4" t="n">
-        <v>8.41238053096451</v>
+        <v>8.373836722077128</v>
       </c>
       <c r="O4" t="n">
-        <v>2.900410407332816</v>
+        <v>2.893758234904417</v>
       </c>
       <c r="P4" t="n">
-        <v>390.6973452958159</v>
+        <v>390.6867253297121</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27513,28 +27651,28 @@
         <v>0.1363</v>
       </c>
       <c r="I5" t="n">
-        <v>0.192902318608848</v>
+        <v>0.1934931904728835</v>
       </c>
       <c r="J5" t="n">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="K5" t="n">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2245798384663924</v>
+        <v>0.2276091157974611</v>
       </c>
       <c r="M5" t="n">
-        <v>2.215360852965937</v>
+        <v>2.206848550429852</v>
       </c>
       <c r="N5" t="n">
-        <v>7.509615158656067</v>
+        <v>7.47268238233642</v>
       </c>
       <c r="O5" t="n">
-        <v>2.740367705008959</v>
+        <v>2.73362074588565</v>
       </c>
       <c r="P5" t="n">
-        <v>397.7312043327744</v>
+        <v>397.7250230521911</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27591,28 +27729,28 @@
         <v>0.1141</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09450770789450512</v>
+        <v>0.09538771582349749</v>
       </c>
       <c r="J6" t="n">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="K6" t="n">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06168416838932811</v>
+        <v>0.06341361389090228</v>
       </c>
       <c r="M6" t="n">
-        <v>2.296517045549573</v>
+        <v>2.28959422923842</v>
       </c>
       <c r="N6" t="n">
-        <v>7.941202175466384</v>
+        <v>7.904017613177519</v>
       </c>
       <c r="O6" t="n">
-        <v>2.818013870701559</v>
+        <v>2.811408474977892</v>
       </c>
       <c r="P6" t="n">
-        <v>394.162513694085</v>
+        <v>394.1533092728728</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27669,28 +27807,28 @@
         <v>0.1124</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01772994132561273</v>
+        <v>0.01841058979938139</v>
       </c>
       <c r="J7" t="n">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="K7" t="n">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001973818711146436</v>
+        <v>0.00215188725592208</v>
       </c>
       <c r="M7" t="n">
-        <v>2.457620500215025</v>
+        <v>2.448463007960615</v>
       </c>
       <c r="N7" t="n">
-        <v>9.29021429385541</v>
+        <v>9.244384365441952</v>
       </c>
       <c r="O7" t="n">
-        <v>3.047985284389577</v>
+        <v>3.040457920353767</v>
       </c>
       <c r="P7" t="n">
-        <v>397.2461004873239</v>
+        <v>397.238980778249</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27747,28 +27885,28 @@
         <v>0.0858</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001906911650719033</v>
+        <v>0.002784091414215874</v>
       </c>
       <c r="J8" t="n">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="K8" t="n">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="L8" t="n">
-        <v>2.280983114788526e-05</v>
+        <v>4.91587150326378e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.369886285500316</v>
+        <v>2.362115343832444</v>
       </c>
       <c r="N8" t="n">
-        <v>9.332507063605497</v>
+        <v>9.288140878549722</v>
       </c>
       <c r="O8" t="n">
-        <v>3.054915230183237</v>
+        <v>3.047645136584921</v>
       </c>
       <c r="P8" t="n">
-        <v>397.7414830850165</v>
+        <v>397.7323126032314</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27825,28 +27963,28 @@
         <v>0.0939</v>
       </c>
       <c r="I9" t="n">
-        <v>0.004109521828181092</v>
+        <v>0.003618070893898325</v>
       </c>
       <c r="J9" t="n">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="K9" t="n">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="L9" t="n">
-        <v>9.465294480437425e-05</v>
+        <v>7.420725956475138e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>2.525231779993881</v>
+        <v>2.513666128763758</v>
       </c>
       <c r="N9" t="n">
-        <v>10.44423183527901</v>
+        <v>10.39104453512308</v>
       </c>
       <c r="O9" t="n">
-        <v>3.231753678001931</v>
+        <v>3.223514314397111</v>
       </c>
       <c r="P9" t="n">
-        <v>397.9102417626843</v>
+        <v>397.9153777695664</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27884,7 +28022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J574"/>
+  <dimension ref="A1:J577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57727,6 +57865,162 @@
         </is>
       </c>
     </row>
+    <row r="575">
+      <c r="A575" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>-35.021048824254954,173.86593718783743</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>-35.02093680345011,173.86682276908022</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>-35.02082887570778,173.86770394607066</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>-35.02068630198093,173.86853464684432</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>-35.02050525505357,173.86934606527552</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>-35.02023220977412,173.87012302828035</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>-35.019862634990645,173.87079699898564</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>-35.01935586013037,173.87134141116877</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>-35.02104621591462,173.86593696372657</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>-35.02093159382328,173.86682221269353</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>-35.02082753174034,173.86770376160905</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>-35.02068209173377,173.86853342785957</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>-35.02050181603973,173.86934441642006</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>-35.02022991782803,173.87012149818946</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>-35.01986015205787,173.87079429035998</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>-35.019354458822924,173.8713394066669</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>-35.02104225843275,173.8659366236963</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>-35.02093087525405,173.86682213595054</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>-35.02082833812079,173.86770387228603</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>-35.020680425177595,173.86853294534478</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>-35.02050114501265,173.8693440946922</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>-35.0202284952408,173.87012054847793</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>-35.019858071762805,173.87079202097107</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>-35.01935440043512,173.87133932314595</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0051/nzd0051.xlsx
+++ b/data/nzd0051/nzd0051.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J577"/>
+  <dimension ref="A1:J579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21212,6 +21212,78 @@
       <c r="J577" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>385.34</v>
+      </c>
+      <c r="C578" t="n">
+        <v>392.28</v>
+      </c>
+      <c r="D578" t="n">
+        <v>395.82</v>
+      </c>
+      <c r="E578" t="n">
+        <v>403.74</v>
+      </c>
+      <c r="F578" t="n">
+        <v>397.3</v>
+      </c>
+      <c r="G578" t="n">
+        <v>398.63</v>
+      </c>
+      <c r="H578" t="n">
+        <v>398.5</v>
+      </c>
+      <c r="I578" t="n">
+        <v>397.31</v>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>385.08</v>
+      </c>
+      <c r="C579" t="n">
+        <v>392.3</v>
+      </c>
+      <c r="D579" t="n">
+        <v>395.72</v>
+      </c>
+      <c r="E579" t="n">
+        <v>403.81</v>
+      </c>
+      <c r="F579" t="n">
+        <v>397.47</v>
+      </c>
+      <c r="G579" t="n">
+        <v>398.75</v>
+      </c>
+      <c r="H579" t="n">
+        <v>398.41</v>
+      </c>
+      <c r="I579" t="n">
+        <v>397.5</v>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -21226,7 +21298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B602"/>
+  <dimension ref="A1:B604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27249,6 +27321,26 @@
       </c>
       <c r="B602" t="n">
         <v>0.08</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B603" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B604" t="n">
+        <v>-0.53</v>
       </c>
     </row>
   </sheetData>
@@ -27417,28 +27509,28 @@
         <v>0.097</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1131089991672911</v>
+        <v>0.1138789199542865</v>
       </c>
       <c r="J2" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K2" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03463157815711515</v>
+        <v>0.03533932387189609</v>
       </c>
       <c r="M2" t="n">
-        <v>3.708162225569205</v>
+        <v>3.699861713606853</v>
       </c>
       <c r="N2" t="n">
-        <v>20.97552256079195</v>
+        <v>20.90757913713617</v>
       </c>
       <c r="O2" t="n">
-        <v>4.579904208691701</v>
+        <v>4.572480632778686</v>
       </c>
       <c r="P2" t="n">
-        <v>380.9968094008959</v>
+        <v>380.988731867319</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27495,28 +27587,28 @@
         <v>0.1099</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1761642840172432</v>
+        <v>0.1769330072434104</v>
       </c>
       <c r="J3" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K3" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1473948839637066</v>
+        <v>0.1494033095188999</v>
       </c>
       <c r="M3" t="n">
-        <v>2.51264653933436</v>
+        <v>2.507698641755864</v>
       </c>
       <c r="N3" t="n">
-        <v>10.55841954825643</v>
+        <v>10.52644971150299</v>
       </c>
       <c r="O3" t="n">
-        <v>3.249372177553139</v>
+        <v>3.244449061320426</v>
       </c>
       <c r="P3" t="n">
-        <v>386.3714781211385</v>
+        <v>386.363413092981</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27573,28 +27665,28 @@
         <v>0.1301</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1511834056145392</v>
+        <v>0.1518469177474402</v>
       </c>
       <c r="J4" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K4" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1383316522119623</v>
+        <v>0.140245974863775</v>
       </c>
       <c r="M4" t="n">
-        <v>1.858781868503596</v>
+        <v>1.856220233015264</v>
       </c>
       <c r="N4" t="n">
-        <v>8.373836722077128</v>
+        <v>8.348270354167912</v>
       </c>
       <c r="O4" t="n">
-        <v>2.893758234904417</v>
+        <v>2.889337355548485</v>
       </c>
       <c r="P4" t="n">
-        <v>390.6867253297121</v>
+        <v>390.6797641443544</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27651,28 +27743,28 @@
         <v>0.1363</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1934931904728835</v>
+        <v>0.1940368086531969</v>
       </c>
       <c r="J5" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K5" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2276091157974611</v>
+        <v>0.2298888476498999</v>
       </c>
       <c r="M5" t="n">
-        <v>2.206848550429852</v>
+        <v>2.201969931032145</v>
       </c>
       <c r="N5" t="n">
-        <v>7.47268238233642</v>
+        <v>7.44911170268163</v>
       </c>
       <c r="O5" t="n">
-        <v>2.73362074588565</v>
+        <v>2.729306084462062</v>
       </c>
       <c r="P5" t="n">
-        <v>397.7250230521911</v>
+        <v>397.7193196937064</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27729,28 +27821,28 @@
         <v>0.1141</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09538771582349749</v>
+        <v>0.09582014780007153</v>
       </c>
       <c r="J6" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K6" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06341361389090228</v>
+        <v>0.06439932355719935</v>
       </c>
       <c r="M6" t="n">
-        <v>2.28959422923842</v>
+        <v>2.284125128656778</v>
       </c>
       <c r="N6" t="n">
-        <v>7.904017613177519</v>
+        <v>7.878138753219805</v>
       </c>
       <c r="O6" t="n">
-        <v>2.811408474977892</v>
+        <v>2.806802229089147</v>
       </c>
       <c r="P6" t="n">
-        <v>394.1533092728728</v>
+        <v>394.1487723967989</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27807,28 +27899,28 @@
         <v>0.1124</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01841058979938139</v>
+        <v>0.01904647665779766</v>
       </c>
       <c r="J7" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K7" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00215188725592208</v>
+        <v>0.002319535675576523</v>
       </c>
       <c r="M7" t="n">
-        <v>2.448463007960615</v>
+        <v>2.443363921069189</v>
       </c>
       <c r="N7" t="n">
-        <v>9.244384365441952</v>
+        <v>9.215532616378109</v>
       </c>
       <c r="O7" t="n">
-        <v>3.040457920353767</v>
+        <v>3.035709573786351</v>
       </c>
       <c r="P7" t="n">
-        <v>397.238980778249</v>
+        <v>397.2323093760114</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27885,28 +27977,28 @@
         <v>0.0858</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002784091414215874</v>
+        <v>0.003214871352863696</v>
       </c>
       <c r="J8" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K8" t="n">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="L8" t="n">
-        <v>4.91587150326378e-05</v>
+        <v>6.603776019686869e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.362115343832444</v>
+        <v>2.356163368093726</v>
       </c>
       <c r="N8" t="n">
-        <v>9.288140878549722</v>
+        <v>9.257388634660145</v>
       </c>
       <c r="O8" t="n">
-        <v>3.047645136584921</v>
+        <v>3.04259570673794</v>
       </c>
       <c r="P8" t="n">
-        <v>397.7323126032314</v>
+        <v>397.7277956799314</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27963,28 +28055,28 @@
         <v>0.0939</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003618070893898325</v>
+        <v>0.003215269286093037</v>
       </c>
       <c r="J9" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K9" t="n">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="L9" t="n">
-        <v>7.420725956475138e-05</v>
+        <v>5.9045406218039e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>2.513666128763758</v>
+        <v>2.506259231810935</v>
       </c>
       <c r="N9" t="n">
-        <v>10.39104453512308</v>
+        <v>10.35631519124631</v>
       </c>
       <c r="O9" t="n">
-        <v>3.223514314397111</v>
+        <v>3.218122929790954</v>
       </c>
       <c r="P9" t="n">
-        <v>397.9153777695664</v>
+        <v>397.9196013033306</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28022,7 +28114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J577"/>
+  <dimension ref="A1:J579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58021,6 +58113,110 @@
         </is>
       </c>
     </row>
+    <row r="578">
+      <c r="A578" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>-35.02104099923399,173.86593651550487</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>-35.020931324359815,173.8668221839149</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>-35.02082771093601,173.86770378620392</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>-35.02068103917197,173.86853312311337</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>-35.02050517117519,173.86934602505954</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>-35.02022841620816,173.87012049571618</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>-35.01986142707741,173.87079568127584</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>-35.01935621045722,173.87134191229427</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>-35.02104333774599,173.86593671643183</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>-35.020931144717515,173.86682216472917</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>-35.0208286069143,173.86770390917835</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>-35.020680425177595,173.86853294534478</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>-35.02050374524263,173.86934534138774</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>-35.02022746781668,173.87011986257517</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>-35.01986203103402,173.87079634013074</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>-35.01935510108885,173.87134032539691</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
